--- a/employee_surveys/040_employee_recognition_program_intake_form--employee_surveys.xlsx
+++ b/employee_surveys/040_employee_recognition_program_intake_form--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>employee_nominations</t>
+          <t>Employee Nominations</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>employee_nominations</t>
+          <t>Reason for Nomination</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>recognition_type</t>
+          <t>Recognition Type</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nomination_date</t>
+          <t>Nomination Date</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nomination_date</t>
+          <t>Nomination Period</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,21 +630,159 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>employee_recognition_program_intute_form_6</t>
+          <t>employee_recognition_program_intake_form_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>employee_nominations</t>
+          <t>Nomination Frequency</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>employee_recognition_program_intake_form_7</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Nomination Description</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>employee_recognition_program_intake_form_8</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Employee Name</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>employee_recognition_program_intake_form_9</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>employee_recognition_program_intake_form_10</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Team Name</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>employee_recognition_program_intake_form_11</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Team Members</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>employee_recognition_program_intake_form_12</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Additional Comments</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -661,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -734,6 +872,57 @@
       <c r="C4" t="inlineStr">
         <is>
           <t>Gift</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>employee_recognition_program_intake_form_6_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>employee_recognition_program_intake_form_6_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>occasional</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Occasional</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>employee_recognition_program_intake_form_6_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>one-time</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>One-time</t>
         </is>
       </c>
     </row>
